--- a/experiments/forecasting/forecasting_NBEATS.xlsx
+++ b/experiments/forecasting/forecasting_NBEATS.xlsx
@@ -13,11 +13,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ndUPC_NBEATS" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mUPC_NBEATS" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rUPC_NBEATS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPCP_NBEATS" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="augmented_NBEATS" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="r+r_NBEATS" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="descriptive" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="per_seed_NBEATS" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="noSPCP_NBEATS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPCP_NBEATS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="augmented_NBEATS" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="r+r_NBEATS" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="descriptive" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="per_seed_NBEATS" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,7 +568,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>synthetic (mUPC): noUPC + mapped UPC (= Ch.5 noSPCP)</t>
+          <t>synthetic (mUPC): noUPC + mapped UPC</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -615,7 +616,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SPCP_NBEATS</t>
+          <t>noSPCP_NBEATS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -625,26 +626,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>synthetic (SPCP): VA-generated appliance PCPs</t>
+          <t>synthetic (noSPCP): Ch.5 baseline, copied real PCPs + mapped UPC (own simulation)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.0969</v>
+        <v>0.987</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0094</v>
+        <v>1.0447</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8498</v>
+        <v>0.8108</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9117</v>
+        <v>0.9014</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>augmented_NBEATS</t>
+          <t>SPCP_NBEATS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -654,48 +655,77 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>augmented: noSPCP + SPCP</t>
+          <t>synthetic (SPCP): VA-generated appliance PCPs</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.0033</v>
+        <v>1.0144</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9936</v>
+        <v>1.0512</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8089</v>
+        <v>0.8229</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9277</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>augmented_NBEATS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>augmented: noSPCP + SPCP</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9786</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.0511</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9046999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>r+r_NBEATS</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>NBEATS</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>r+r: real duplicated (data-volume control)</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
         <v>0.9645</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" t="n">
         <v>1.0543</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" t="n">
         <v>0.8008</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G10" t="n">
         <v>0.9108000000000001</v>
       </c>
     </row>
@@ -710,605 +740,320 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>rel%_vs_real</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CI95_lo</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>CI95_hi</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>better/N</t>
+          <t>Konfig:</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NBEATS</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9455</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>experiment: r+r_NBEATS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NBEATS</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>RMSSE</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0.7932</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>model: NBEATS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NBEATS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>noUPC</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1.1029</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-17.4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-32.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>3/10</t>
+          <t>training data: r+r: real duplicated (data-volume control)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NBEATS</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>noUPC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>RMSSE</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.8928</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-12.3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-20.4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2/10</t>
+          <t>input_chunk=192 output_chunk=96 epochs=50 batch=32 season(m)=96</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NBEATS</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ndUPC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.8924</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>6/10</t>
+          <t>aggregate: meter1+2+3 (3-phase mains), 15min mean</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NBEATS</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ndUPC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>RMSSE</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.7907999999999999</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>5/10</t>
+          <t>metrics: MASE (MAE-based) and RMSSE (RMSE-based), both scaled by seasonal-naive</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NBEATS</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>mUPC</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.9645</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-4</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-13.1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2/10</t>
+          <t>transfer: train -&gt; test on real UNSEEN households</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NBEATS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>mUPC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>RMSSE</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.7977</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>4/10</t>
+          <t>seeds: 10 (per-household value averaged over seeds)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NBEATS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>rUPC</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1.0159</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-18.2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NBEATS</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>rUPC</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>RMSSE</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.8349</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-16.7</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>4/10</t>
+          <t>test households (n=10): ['building11', 'building13', 'building17', 'building19', 'building20', 'building3', 'building5', 'building6', 'building8', 'building9']</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NBEATS</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SPCP</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1.0969</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-16.7</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-30.9</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2/10</t>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>household</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>MASE_mean</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>MASE_std</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>RMSSE_mean</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>RMSSE_std</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NBEATS</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SPCP</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>RMSSE</t>
-        </is>
+          <t>building11</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4669</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0825</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8498</v>
+        <v>0.313</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-21.1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
+        <v>0.0289</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NBEATS</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>augmented</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
+          <t>building13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.0755</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.1065</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0033</v>
+        <v>1.0024</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-17</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2/10</t>
-        </is>
+        <v>0.0541</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NBEATS</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>augmented</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>RMSSE</t>
-        </is>
+          <t>building17</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.8917</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.2498</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8089</v>
+        <v>0.5501</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-12.2</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
+        <v>0.1388</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NBEATS</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>r+r</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
+          <t>building19</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.0546</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.076</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9645</v>
+        <v>0.9433</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
+        <v>0.0602</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NBEATS</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>r+r</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>RMSSE</t>
-        </is>
+          <t>building20</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.2241</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1849</v>
       </c>
       <c r="D17" t="n">
+        <v>1.0125</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.1459</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>building3</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.4735</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0167</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>building5</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.3745</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9181</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>building6</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.0539</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.07770000000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0304</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>building8</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.0876</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.2049</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.8626</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1554</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>building9</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.9929</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.0745</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.9034</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0219</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>aggregate (mean over households)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.9645</v>
+      </c>
+      <c r="D23" t="n">
         <v>0.8008</v>
       </c>
-      <c r="E17" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>aggregate (median over households)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.0543</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.9108000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1322,12 +1067,692 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M209"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>rel%_vs_real</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CI95_lo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>CI95_hi</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>better/N</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9455</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.7932</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>noUPC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.1029</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-32.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>noUPC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8928</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ndUPC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8924</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ndUPC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7907999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mUPC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.9645</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mUPC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7977</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rUPC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0159</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-18.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>rUPC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8349</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>noSPCP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>noSPCP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.8108</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SPCP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.0144</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-17.7</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SPCP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.8229</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>augmented</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.9786</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>augmented</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>r+r</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.9645</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NBEATS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>r+r</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.8008</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M235"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>Per-seed values (NBEATS) — rows: households; cols: seed0..seed9; MASE and RMSSE blocks per condition. Reconstructed from raw/*.npy.</t>
         </is>
       </c>
@@ -6375,7 +6800,7 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>SPCP — MASE</t>
+          <t>noSPCP — MASE</t>
         </is>
       </c>
     </row>
@@ -6453,40 +6878,40 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.507</v>
+        <v>0.6236</v>
       </c>
       <c r="C135" t="n">
-        <v>0.6358</v>
+        <v>0.3961</v>
       </c>
       <c r="D135" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.4575</v>
       </c>
       <c r="E135" t="n">
-        <v>0.5969</v>
+        <v>0.5137</v>
       </c>
       <c r="F135" t="n">
-        <v>0.4716</v>
+        <v>0.5579</v>
       </c>
       <c r="G135" t="n">
-        <v>0.5904</v>
+        <v>0.4877</v>
       </c>
       <c r="H135" t="n">
-        <v>0.5627</v>
+        <v>0.4974</v>
       </c>
       <c r="I135" t="n">
-        <v>0.5853</v>
+        <v>0.4805</v>
       </c>
       <c r="J135" t="n">
-        <v>0.8139</v>
+        <v>0.4451</v>
       </c>
       <c r="K135" t="n">
-        <v>0.4437</v>
+        <v>0.5634</v>
       </c>
       <c r="L135" t="n">
-        <v>0.6034</v>
+        <v>0.5023</v>
       </c>
       <c r="M135" t="n">
-        <v>0.129</v>
+        <v>0.0658</v>
       </c>
     </row>
     <row r="136">
@@ -6496,40 +6921,40 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1.4688</v>
+        <v>0.9998</v>
       </c>
       <c r="C136" t="n">
-        <v>1.6025</v>
+        <v>1.0254</v>
       </c>
       <c r="D136" t="n">
-        <v>1.2626</v>
+        <v>1.1385</v>
       </c>
       <c r="E136" t="n">
-        <v>1.3566</v>
+        <v>1.2138</v>
       </c>
       <c r="F136" t="n">
-        <v>1.1481</v>
+        <v>0.9731</v>
       </c>
       <c r="G136" t="n">
-        <v>1.2213</v>
+        <v>1.1181</v>
       </c>
       <c r="H136" t="n">
-        <v>1.341</v>
+        <v>1.0516</v>
       </c>
       <c r="I136" t="n">
-        <v>1.2168</v>
+        <v>1.1272</v>
       </c>
       <c r="J136" t="n">
-        <v>1.4688</v>
+        <v>1.1334</v>
       </c>
       <c r="K136" t="n">
-        <v>1.473</v>
+        <v>1.1394</v>
       </c>
       <c r="L136" t="n">
-        <v>1.356</v>
+        <v>1.092</v>
       </c>
       <c r="M136" t="n">
-        <v>0.1451</v>
+        <v>0.0757</v>
       </c>
     </row>
     <row r="137">
@@ -6539,40 +6964,40 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.6783</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="C137" t="n">
-        <v>0.8963</v>
+        <v>1.0248</v>
       </c>
       <c r="D137" t="n">
-        <v>1.0672</v>
+        <v>0.9842</v>
       </c>
       <c r="E137" t="n">
-        <v>0.8507</v>
+        <v>0.9113</v>
       </c>
       <c r="F137" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.705</v>
       </c>
       <c r="G137" t="n">
-        <v>0.8304</v>
+        <v>0.9931</v>
       </c>
       <c r="H137" t="n">
-        <v>0.713</v>
+        <v>0.8026</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.8153</v>
       </c>
       <c r="J137" t="n">
-        <v>1.0532</v>
+        <v>1.137</v>
       </c>
       <c r="K137" t="n">
-        <v>0.842</v>
+        <v>0.7</v>
       </c>
       <c r="L137" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.8839</v>
       </c>
       <c r="M137" t="n">
-        <v>0.1419</v>
+        <v>0.1482</v>
       </c>
     </row>
     <row r="138">
@@ -6582,40 +7007,40 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.889</v>
+        <v>1.1018</v>
       </c>
       <c r="C138" t="n">
-        <v>1.061</v>
+        <v>1.2489</v>
       </c>
       <c r="D138" t="n">
-        <v>1.0826</v>
+        <v>1.0085</v>
       </c>
       <c r="E138" t="n">
-        <v>1.0151</v>
+        <v>1.0391</v>
       </c>
       <c r="F138" t="n">
-        <v>0.9026</v>
+        <v>1.3033</v>
       </c>
       <c r="G138" t="n">
-        <v>1.0751</v>
+        <v>1.1566</v>
       </c>
       <c r="H138" t="n">
-        <v>1.0439</v>
+        <v>1.1326</v>
       </c>
       <c r="I138" t="n">
-        <v>1.1055</v>
+        <v>1.0805</v>
       </c>
       <c r="J138" t="n">
-        <v>1.0901</v>
+        <v>1.19</v>
       </c>
       <c r="K138" t="n">
-        <v>1.0055</v>
+        <v>1.0787</v>
       </c>
       <c r="L138" t="n">
-        <v>1.027</v>
+        <v>1.134</v>
       </c>
       <c r="M138" t="n">
-        <v>0.0761</v>
+        <v>0.0926</v>
       </c>
     </row>
     <row r="139">
@@ -6625,40 +7050,40 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1.3325</v>
+        <v>1.1275</v>
       </c>
       <c r="C139" t="n">
-        <v>1.3955</v>
+        <v>1.3801</v>
       </c>
       <c r="D139" t="n">
-        <v>1.6158</v>
+        <v>1.0988</v>
       </c>
       <c r="E139" t="n">
-        <v>1.9099</v>
+        <v>1.1089</v>
       </c>
       <c r="F139" t="n">
-        <v>2.0043</v>
+        <v>1.6673</v>
       </c>
       <c r="G139" t="n">
-        <v>1.5975</v>
+        <v>1.2107</v>
       </c>
       <c r="H139" t="n">
-        <v>1.4894</v>
+        <v>1.0263</v>
       </c>
       <c r="I139" t="n">
-        <v>1.3765</v>
+        <v>1.2648</v>
       </c>
       <c r="J139" t="n">
-        <v>1.6909</v>
+        <v>1.0914</v>
       </c>
       <c r="K139" t="n">
-        <v>1.9363</v>
+        <v>1.6764</v>
       </c>
       <c r="L139" t="n">
-        <v>1.6349</v>
+        <v>1.2652</v>
       </c>
       <c r="M139" t="n">
-        <v>0.246</v>
+        <v>0.237</v>
       </c>
     </row>
     <row r="140">
@@ -6668,40 +7093,40 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4557</v>
+        <v>0.6073</v>
       </c>
       <c r="C140" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.6876</v>
       </c>
       <c r="D140" t="n">
-        <v>0.6113</v>
+        <v>0.5491</v>
       </c>
       <c r="E140" t="n">
-        <v>0.4955</v>
+        <v>0.4307</v>
       </c>
       <c r="F140" t="n">
-        <v>0.5707</v>
+        <v>0.5807</v>
       </c>
       <c r="G140" t="n">
-        <v>0.4931</v>
+        <v>0.63</v>
       </c>
       <c r="H140" t="n">
-        <v>0.5481</v>
+        <v>0.4368</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4714</v>
+        <v>0.4637</v>
       </c>
       <c r="J140" t="n">
-        <v>0.5985</v>
+        <v>0.5724</v>
       </c>
       <c r="K140" t="n">
-        <v>0.6127</v>
+        <v>0.6272</v>
       </c>
       <c r="L140" t="n">
-        <v>0.5457</v>
+        <v>0.5585</v>
       </c>
       <c r="M140" t="n">
-        <v>0.0616</v>
+        <v>0.0881</v>
       </c>
     </row>
     <row r="141">
@@ -6711,40 +7136,40 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2.0766</v>
+        <v>1.2576</v>
       </c>
       <c r="C141" t="n">
-        <v>2.0674</v>
+        <v>1.2496</v>
       </c>
       <c r="D141" t="n">
-        <v>1.9018</v>
+        <v>1.3723</v>
       </c>
       <c r="E141" t="n">
-        <v>1.9962</v>
+        <v>1.2033</v>
       </c>
       <c r="F141" t="n">
-        <v>2.0748</v>
+        <v>1.5787</v>
       </c>
       <c r="G141" t="n">
-        <v>1.5569</v>
+        <v>1.302</v>
       </c>
       <c r="H141" t="n">
-        <v>1.6789</v>
+        <v>1.4078</v>
       </c>
       <c r="I141" t="n">
-        <v>2.3143</v>
+        <v>1.3209</v>
       </c>
       <c r="J141" t="n">
-        <v>1.9771</v>
+        <v>1.2958</v>
       </c>
       <c r="K141" t="n">
-        <v>2.0767</v>
+        <v>1.205</v>
       </c>
       <c r="L141" t="n">
-        <v>1.9721</v>
+        <v>1.3193</v>
       </c>
       <c r="M141" t="n">
-        <v>0.2167</v>
+        <v>0.1125</v>
       </c>
     </row>
     <row r="142">
@@ -6754,40 +7179,40 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1.1363</v>
+        <v>0.9266</v>
       </c>
       <c r="C142" t="n">
-        <v>0.9498</v>
+        <v>1.0897</v>
       </c>
       <c r="D142" t="n">
-        <v>0.9429999999999999</v>
+        <v>1.0067</v>
       </c>
       <c r="E142" t="n">
-        <v>0.9951</v>
+        <v>0.9372</v>
       </c>
       <c r="F142" t="n">
-        <v>1.0075</v>
+        <v>1.102</v>
       </c>
       <c r="G142" t="n">
-        <v>0.8694</v>
+        <v>1.0845</v>
       </c>
       <c r="H142" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.8965</v>
       </c>
       <c r="I142" t="n">
-        <v>1.0072</v>
+        <v>1.1349</v>
       </c>
       <c r="J142" t="n">
-        <v>1.1053</v>
+        <v>1.0852</v>
       </c>
       <c r="K142" t="n">
-        <v>0.9224</v>
+        <v>1.0078</v>
       </c>
       <c r="L142" t="n">
-        <v>0.9918</v>
+        <v>1.0271</v>
       </c>
       <c r="M142" t="n">
-        <v>0.0805</v>
+        <v>0.0842</v>
       </c>
     </row>
     <row r="143">
@@ -6797,40 +7222,40 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1.0607</v>
+        <v>0.9944</v>
       </c>
       <c r="C143" t="n">
-        <v>1.0904</v>
+        <v>0.9802</v>
       </c>
       <c r="D143" t="n">
-        <v>0.7851</v>
+        <v>1.0806</v>
       </c>
       <c r="E143" t="n">
-        <v>0.8209</v>
+        <v>1.0649</v>
       </c>
       <c r="F143" t="n">
-        <v>0.9212</v>
+        <v>1.0087</v>
       </c>
       <c r="G143" t="n">
-        <v>0.7647</v>
+        <v>1.1824</v>
       </c>
       <c r="H143" t="n">
-        <v>0.9347</v>
+        <v>1.0503</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0626</v>
+        <v>1.1513</v>
       </c>
       <c r="J143" t="n">
-        <v>1.059</v>
+        <v>1.1328</v>
       </c>
       <c r="K143" t="n">
-        <v>1.0796</v>
+        <v>0.9781</v>
       </c>
       <c r="L143" t="n">
-        <v>0.9579</v>
+        <v>1.0624</v>
       </c>
       <c r="M143" t="n">
-        <v>0.1299</v>
+        <v>0.07389999999999999</v>
       </c>
     </row>
     <row r="144">
@@ -6840,46 +7265,46 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.9048</v>
+        <v>0.956</v>
       </c>
       <c r="C144" t="n">
-        <v>0.989</v>
+        <v>1.0746</v>
       </c>
       <c r="D144" t="n">
-        <v>1.0672</v>
+        <v>0.9369</v>
       </c>
       <c r="E144" t="n">
-        <v>1.0482</v>
+        <v>0.9152</v>
       </c>
       <c r="F144" t="n">
-        <v>1.1567</v>
+        <v>1.1197</v>
       </c>
       <c r="G144" t="n">
-        <v>1.0419</v>
+        <v>1.0285</v>
       </c>
       <c r="H144" t="n">
-        <v>1.0542</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="I144" t="n">
-        <v>1.0593</v>
+        <v>1.0368</v>
       </c>
       <c r="J144" t="n">
-        <v>1.0562</v>
+        <v>1.0654</v>
       </c>
       <c r="K144" t="n">
-        <v>1.0955</v>
+        <v>1.1429</v>
       </c>
       <c r="L144" t="n">
-        <v>1.0473</v>
+        <v>1.025</v>
       </c>
       <c r="M144" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0776</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>SPCP — RMSSE</t>
+          <t>noSPCP — RMSSE</t>
         </is>
       </c>
     </row>
@@ -6957,40 +7382,40 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.3171</v>
+        <v>0.3828</v>
       </c>
       <c r="C148" t="n">
-        <v>0.4623</v>
+        <v>0.2741</v>
       </c>
       <c r="D148" t="n">
-        <v>0.5455</v>
+        <v>0.3028</v>
       </c>
       <c r="E148" t="n">
-        <v>0.4061</v>
+        <v>0.3376</v>
       </c>
       <c r="F148" t="n">
-        <v>0.3272</v>
+        <v>0.3488</v>
       </c>
       <c r="G148" t="n">
-        <v>0.4111</v>
+        <v>0.2832</v>
       </c>
       <c r="H148" t="n">
-        <v>0.3727</v>
+        <v>0.3493</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3599</v>
+        <v>0.3148</v>
       </c>
       <c r="J148" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.2821</v>
       </c>
       <c r="K148" t="n">
-        <v>0.337</v>
+        <v>0.3572</v>
       </c>
       <c r="L148" t="n">
-        <v>0.4069</v>
+        <v>0.3233</v>
       </c>
       <c r="M148" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0372</v>
       </c>
     </row>
     <row r="149">
@@ -7000,40 +7425,40 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1.0768</v>
+        <v>1.017</v>
       </c>
       <c r="C149" t="n">
-        <v>1.2129</v>
+        <v>1.0002</v>
       </c>
       <c r="D149" t="n">
-        <v>1.0879</v>
+        <v>1.0492</v>
       </c>
       <c r="E149" t="n">
-        <v>1.1253</v>
+        <v>0.9714</v>
       </c>
       <c r="F149" t="n">
-        <v>1.0374</v>
+        <v>1.1031</v>
       </c>
       <c r="G149" t="n">
-        <v>0.9568</v>
+        <v>0.9377</v>
       </c>
       <c r="H149" t="n">
-        <v>1.0846</v>
+        <v>1.0175</v>
       </c>
       <c r="I149" t="n">
-        <v>1.0481</v>
+        <v>0.9746</v>
       </c>
       <c r="J149" t="n">
-        <v>1.1095</v>
+        <v>1.0362</v>
       </c>
       <c r="K149" t="n">
-        <v>1.1868</v>
+        <v>1.0135</v>
       </c>
       <c r="L149" t="n">
-        <v>1.0926</v>
+        <v>1.012</v>
       </c>
       <c r="M149" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="150">
@@ -7043,40 +7468,40 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4184</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="C150" t="n">
-        <v>0.5219</v>
+        <v>0.5605</v>
       </c>
       <c r="D150" t="n">
-        <v>0.6415</v>
+        <v>0.5844</v>
       </c>
       <c r="E150" t="n">
-        <v>0.5108</v>
+        <v>0.5673</v>
       </c>
       <c r="F150" t="n">
-        <v>0.4547</v>
+        <v>0.4577</v>
       </c>
       <c r="G150" t="n">
-        <v>0.4867</v>
+        <v>0.582</v>
       </c>
       <c r="H150" t="n">
-        <v>0.4485</v>
+        <v>0.4874</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4454</v>
+        <v>0.458</v>
       </c>
       <c r="J150" t="n">
-        <v>0.5699</v>
+        <v>0.6702</v>
       </c>
       <c r="K150" t="n">
-        <v>0.4705</v>
+        <v>0.45</v>
       </c>
       <c r="L150" t="n">
-        <v>0.4968</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="M150" t="n">
-        <v>0.0673</v>
+        <v>0.0723</v>
       </c>
     </row>
     <row r="151">
@@ -7086,40 +7511,40 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.8665</v>
+        <v>0.9728</v>
       </c>
       <c r="C151" t="n">
-        <v>1.0296</v>
+        <v>0.9544</v>
       </c>
       <c r="D151" t="n">
-        <v>0.9073</v>
+        <v>0.8702</v>
       </c>
       <c r="E151" t="n">
-        <v>0.8639</v>
+        <v>0.9506</v>
       </c>
       <c r="F151" t="n">
-        <v>0.8717</v>
+        <v>1.0809</v>
       </c>
       <c r="G151" t="n">
-        <v>0.9584</v>
+        <v>0.9912</v>
       </c>
       <c r="H151" t="n">
-        <v>0.9453</v>
+        <v>0.966</v>
       </c>
       <c r="I151" t="n">
-        <v>0.9488</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="J151" t="n">
-        <v>0.9223</v>
+        <v>0.9981</v>
       </c>
       <c r="K151" t="n">
-        <v>0.8588</v>
+        <v>0.9866</v>
       </c>
       <c r="L151" t="n">
-        <v>0.9173</v>
+        <v>0.97</v>
       </c>
       <c r="M151" t="n">
-        <v>0.0549</v>
+        <v>0.0539</v>
       </c>
     </row>
     <row r="152">
@@ -7129,40 +7554,40 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.9661</v>
+        <v>1.0274</v>
       </c>
       <c r="C152" t="n">
-        <v>0.9981</v>
+        <v>1.0901</v>
       </c>
       <c r="D152" t="n">
-        <v>1.1908</v>
+        <v>1.0106</v>
       </c>
       <c r="E152" t="n">
-        <v>1.2899</v>
+        <v>0.8744</v>
       </c>
       <c r="F152" t="n">
-        <v>1.3863</v>
+        <v>1.4023</v>
       </c>
       <c r="G152" t="n">
-        <v>1.1146</v>
+        <v>0.9848</v>
       </c>
       <c r="H152" t="n">
-        <v>1.0692</v>
+        <v>0.9287</v>
       </c>
       <c r="I152" t="n">
-        <v>1.0872</v>
+        <v>0.9705</v>
       </c>
       <c r="J152" t="n">
-        <v>1.1684</v>
+        <v>0.8499</v>
       </c>
       <c r="K152" t="n">
-        <v>1.381</v>
+        <v>1.4108</v>
       </c>
       <c r="L152" t="n">
-        <v>1.1652</v>
+        <v>1.055</v>
       </c>
       <c r="M152" t="n">
-        <v>0.148</v>
+        <v>0.1983</v>
       </c>
     </row>
     <row r="153">
@@ -7172,40 +7597,40 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4962</v>
+        <v>0.5426</v>
       </c>
       <c r="C153" t="n">
-        <v>0.5296</v>
+        <v>0.5658</v>
       </c>
       <c r="D153" t="n">
-        <v>0.5531</v>
+        <v>0.5291</v>
       </c>
       <c r="E153" t="n">
-        <v>0.5068</v>
+        <v>0.4596</v>
       </c>
       <c r="F153" t="n">
-        <v>0.5556</v>
+        <v>0.5329</v>
       </c>
       <c r="G153" t="n">
-        <v>0.5124</v>
+        <v>0.5897</v>
       </c>
       <c r="H153" t="n">
-        <v>0.5159</v>
+        <v>0.4809</v>
       </c>
       <c r="I153" t="n">
-        <v>0.489</v>
+        <v>0.5216</v>
       </c>
       <c r="J153" t="n">
-        <v>0.5582</v>
+        <v>0.5421</v>
       </c>
       <c r="K153" t="n">
-        <v>0.5578</v>
+        <v>0.5616</v>
       </c>
       <c r="L153" t="n">
-        <v>0.5274</v>
+        <v>0.5326</v>
       </c>
       <c r="M153" t="n">
-        <v>0.027</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="154">
@@ -7215,40 +7640,40 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1.4177</v>
+        <v>1.0017</v>
       </c>
       <c r="C154" t="n">
-        <v>1.3934</v>
+        <v>0.9915</v>
       </c>
       <c r="D154" t="n">
-        <v>1.2516</v>
+        <v>0.9146</v>
       </c>
       <c r="E154" t="n">
-        <v>1.3518</v>
+        <v>0.788</v>
       </c>
       <c r="F154" t="n">
-        <v>1.3882</v>
+        <v>1.0235</v>
       </c>
       <c r="G154" t="n">
-        <v>1.0569</v>
+        <v>0.8815</v>
       </c>
       <c r="H154" t="n">
-        <v>1.155</v>
+        <v>1.0096</v>
       </c>
       <c r="I154" t="n">
-        <v>1.3468</v>
+        <v>0.8297</v>
       </c>
       <c r="J154" t="n">
-        <v>1.3657</v>
+        <v>0.8956</v>
       </c>
       <c r="K154" t="n">
-        <v>1.3545</v>
+        <v>0.7751</v>
       </c>
       <c r="L154" t="n">
-        <v>1.3082</v>
+        <v>0.9111</v>
       </c>
       <c r="M154" t="n">
-        <v>0.1175</v>
+        <v>0.09329999999999999</v>
       </c>
     </row>
     <row r="155">
@@ -7258,40 +7683,40 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.9509</v>
+        <v>0.948</v>
       </c>
       <c r="C155" t="n">
-        <v>0.9414</v>
+        <v>0.9927</v>
       </c>
       <c r="D155" t="n">
-        <v>0.9134</v>
+        <v>1.0428</v>
       </c>
       <c r="E155" t="n">
-        <v>0.9847</v>
+        <v>0.9861</v>
       </c>
       <c r="F155" t="n">
-        <v>0.9588</v>
+        <v>1.0433</v>
       </c>
       <c r="G155" t="n">
-        <v>0.9443</v>
+        <v>1.0076</v>
       </c>
       <c r="H155" t="n">
-        <v>0.9314</v>
+        <v>0.9959</v>
       </c>
       <c r="I155" t="n">
-        <v>0.9235</v>
+        <v>1.0223</v>
       </c>
       <c r="J155" t="n">
-        <v>0.9271</v>
+        <v>1.0142</v>
       </c>
       <c r="K155" t="n">
-        <v>0.8852</v>
+        <v>1.0693</v>
       </c>
       <c r="L155" t="n">
-        <v>0.9361</v>
+        <v>1.0122</v>
       </c>
       <c r="M155" t="n">
-        <v>0.027</v>
+        <v>0.0345</v>
       </c>
     </row>
     <row r="156">
@@ -7301,40 +7726,40 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.8403</v>
+        <v>0.8007</v>
       </c>
       <c r="C156" t="n">
-        <v>0.7699</v>
+        <v>0.7837</v>
       </c>
       <c r="D156" t="n">
-        <v>0.6055</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="E156" t="n">
-        <v>0.6296</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F156" t="n">
-        <v>0.74</v>
+        <v>0.9087</v>
       </c>
       <c r="G156" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="H156" t="n">
-        <v>0.7409</v>
+        <v>0.8433</v>
       </c>
       <c r="I156" t="n">
-        <v>0.8423</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="J156" t="n">
-        <v>0.8233</v>
+        <v>0.7937</v>
       </c>
       <c r="K156" t="n">
-        <v>0.8468</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="L156" t="n">
-        <v>0.7416</v>
+        <v>0.8683</v>
       </c>
       <c r="M156" t="n">
-        <v>0.1036</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="157">
@@ -7344,46 +7769,46 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.8691</v>
+        <v>0.8719</v>
       </c>
       <c r="C157" t="n">
-        <v>0.8787</v>
+        <v>0.863</v>
       </c>
       <c r="D157" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.8989</v>
       </c>
       <c r="E157" t="n">
-        <v>0.8914</v>
+        <v>0.8525</v>
       </c>
       <c r="F157" t="n">
-        <v>0.9404</v>
+        <v>0.8873</v>
       </c>
       <c r="G157" t="n">
-        <v>0.903</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="H157" t="n">
-        <v>0.947</v>
+        <v>0.8913</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8938</v>
+        <v>0.8965</v>
       </c>
       <c r="J157" t="n">
-        <v>0.8891</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="K157" t="n">
-        <v>0.9165</v>
+        <v>0.9425</v>
       </c>
       <c r="L157" t="n">
-        <v>0.9061</v>
+        <v>0.8917</v>
       </c>
       <c r="M157" t="n">
-        <v>0.0267</v>
+        <v>0.0287</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>augmented — MASE</t>
+          <t>SPCP — MASE</t>
         </is>
       </c>
     </row>
@@ -7461,40 +7886,40 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.4739</v>
+        <v>0.5266</v>
       </c>
       <c r="C161" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5334</v>
       </c>
       <c r="D161" t="n">
-        <v>0.4168</v>
+        <v>0.4688</v>
       </c>
       <c r="E161" t="n">
-        <v>0.5738</v>
+        <v>0.5012</v>
       </c>
       <c r="F161" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="G161" t="n">
-        <v>0.5171</v>
+        <v>0.5145</v>
       </c>
       <c r="H161" t="n">
-        <v>0.6176</v>
+        <v>0.6219</v>
       </c>
       <c r="I161" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.5901</v>
       </c>
       <c r="J161" t="n">
-        <v>0.9579</v>
+        <v>0.6145</v>
       </c>
       <c r="K161" t="n">
-        <v>0.405</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="L161" t="n">
-        <v>0.5757</v>
+        <v>0.5659</v>
       </c>
       <c r="M161" t="n">
-        <v>0.1596</v>
+        <v>0.0646</v>
       </c>
     </row>
     <row r="162">
@@ -7504,40 +7929,40 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1.1077</v>
+        <v>1.0847</v>
       </c>
       <c r="C162" t="n">
-        <v>1.4057</v>
+        <v>0.9818</v>
       </c>
       <c r="D162" t="n">
-        <v>1.0382</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="E162" t="n">
-        <v>1.2063</v>
+        <v>1.3102</v>
       </c>
       <c r="F162" t="n">
-        <v>1.2241</v>
+        <v>1.1974</v>
       </c>
       <c r="G162" t="n">
-        <v>1.1834</v>
+        <v>1.135</v>
       </c>
       <c r="H162" t="n">
-        <v>1.001</v>
+        <v>1.0855</v>
       </c>
       <c r="I162" t="n">
-        <v>1.0325</v>
+        <v>1.0465</v>
       </c>
       <c r="J162" t="n">
-        <v>1.2189</v>
+        <v>1.1801</v>
       </c>
       <c r="K162" t="n">
-        <v>0.8974</v>
+        <v>1.2588</v>
       </c>
       <c r="L162" t="n">
-        <v>1.1315</v>
+        <v>1.127</v>
       </c>
       <c r="M162" t="n">
-        <v>0.1455</v>
+        <v>0.1098</v>
       </c>
     </row>
     <row r="163">
@@ -7547,40 +7972,40 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.6151</v>
+        <v>1.1599</v>
       </c>
       <c r="C163" t="n">
-        <v>0.514</v>
+        <v>1.1561</v>
       </c>
       <c r="D163" t="n">
-        <v>0.6687</v>
+        <v>0.8754</v>
       </c>
       <c r="E163" t="n">
-        <v>0.6873</v>
+        <v>1.2955</v>
       </c>
       <c r="F163" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.9609</v>
       </c>
       <c r="G163" t="n">
-        <v>0.9105</v>
+        <v>0.7181</v>
       </c>
       <c r="H163" t="n">
-        <v>0.9255</v>
+        <v>1.0371</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8774</v>
+        <v>1.1221</v>
       </c>
       <c r="J163" t="n">
-        <v>0.9384</v>
+        <v>0.8852</v>
       </c>
       <c r="K163" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9681</v>
       </c>
       <c r="L163" t="n">
-        <v>0.7688</v>
+        <v>1.0178</v>
       </c>
       <c r="M163" t="n">
-        <v>0.1631</v>
+        <v>0.1703</v>
       </c>
     </row>
     <row r="164">
@@ -7590,40 +8015,40 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>1.4322</v>
+        <v>0.9768</v>
       </c>
       <c r="C164" t="n">
-        <v>1.224</v>
+        <v>1.0605</v>
       </c>
       <c r="D164" t="n">
-        <v>1.2923</v>
+        <v>1.1073</v>
       </c>
       <c r="E164" t="n">
-        <v>1.0961</v>
+        <v>1.1196</v>
       </c>
       <c r="F164" t="n">
-        <v>1.1103</v>
+        <v>0.9977</v>
       </c>
       <c r="G164" t="n">
-        <v>1.0107</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="H164" t="n">
-        <v>1.1329</v>
+        <v>1.2604</v>
       </c>
       <c r="I164" t="n">
-        <v>0.9943</v>
+        <v>1.1133</v>
       </c>
       <c r="J164" t="n">
-        <v>1.1418</v>
+        <v>1.2921</v>
       </c>
       <c r="K164" t="n">
-        <v>1.0227</v>
+        <v>0.9828</v>
       </c>
       <c r="L164" t="n">
-        <v>1.1457</v>
+        <v>1.0846</v>
       </c>
       <c r="M164" t="n">
-        <v>0.1374</v>
+        <v>0.1196</v>
       </c>
     </row>
     <row r="165">
@@ -7633,40 +8058,40 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1.3076</v>
+        <v>1.743</v>
       </c>
       <c r="C165" t="n">
-        <v>1.6894</v>
+        <v>1.2144</v>
       </c>
       <c r="D165" t="n">
-        <v>1.5084</v>
+        <v>1.5346</v>
       </c>
       <c r="E165" t="n">
-        <v>1.4174</v>
+        <v>1.3052</v>
       </c>
       <c r="F165" t="n">
-        <v>1.5758</v>
+        <v>1.4062</v>
       </c>
       <c r="G165" t="n">
-        <v>1.1255</v>
+        <v>1.2282</v>
       </c>
       <c r="H165" t="n">
-        <v>1.0324</v>
+        <v>1.1687</v>
       </c>
       <c r="I165" t="n">
-        <v>1.2502</v>
+        <v>1.5</v>
       </c>
       <c r="J165" t="n">
-        <v>1.0277</v>
+        <v>1.1681</v>
       </c>
       <c r="K165" t="n">
-        <v>0.9205</v>
+        <v>1.096</v>
       </c>
       <c r="L165" t="n">
-        <v>1.2855</v>
+        <v>1.3364</v>
       </c>
       <c r="M165" t="n">
-        <v>0.2594</v>
+        <v>0.2049</v>
       </c>
     </row>
     <row r="166">
@@ -7676,40 +8101,40 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.5239</v>
+        <v>0.4784</v>
       </c>
       <c r="C166" t="n">
-        <v>0.4563</v>
+        <v>0.519</v>
       </c>
       <c r="D166" t="n">
-        <v>0.4264</v>
+        <v>0.447</v>
       </c>
       <c r="E166" t="n">
-        <v>0.5037</v>
+        <v>0.4874</v>
       </c>
       <c r="F166" t="n">
-        <v>0.4911</v>
+        <v>0.556</v>
       </c>
       <c r="G166" t="n">
-        <v>0.3885</v>
+        <v>0.4389</v>
       </c>
       <c r="H166" t="n">
-        <v>0.5065</v>
+        <v>0.4915</v>
       </c>
       <c r="I166" t="n">
-        <v>0.4952</v>
+        <v>0.5234</v>
       </c>
       <c r="J166" t="n">
-        <v>0.4306</v>
+        <v>0.499</v>
       </c>
       <c r="K166" t="n">
-        <v>0.5837</v>
+        <v>0.5802</v>
       </c>
       <c r="L166" t="n">
-        <v>0.4806</v>
+        <v>0.5021</v>
       </c>
       <c r="M166" t="n">
-        <v>0.0563</v>
+        <v>0.0443</v>
       </c>
     </row>
     <row r="167">
@@ -7719,40 +8144,40 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>1.3902</v>
+        <v>1.1917</v>
       </c>
       <c r="C167" t="n">
-        <v>2.1267</v>
+        <v>1.2217</v>
       </c>
       <c r="D167" t="n">
-        <v>1.2491</v>
+        <v>1.4734</v>
       </c>
       <c r="E167" t="n">
-        <v>1.298</v>
+        <v>1.3669</v>
       </c>
       <c r="F167" t="n">
-        <v>2.0475</v>
+        <v>1.3877</v>
       </c>
       <c r="G167" t="n">
-        <v>2.2531</v>
+        <v>1.6563</v>
       </c>
       <c r="H167" t="n">
-        <v>1.7611</v>
+        <v>1.2953</v>
       </c>
       <c r="I167" t="n">
-        <v>1.7684</v>
+        <v>1.2135</v>
       </c>
       <c r="J167" t="n">
-        <v>2.2751</v>
+        <v>1.7736</v>
       </c>
       <c r="K167" t="n">
-        <v>1.1346</v>
+        <v>1.0582</v>
       </c>
       <c r="L167" t="n">
-        <v>1.7304</v>
+        <v>1.3638</v>
       </c>
       <c r="M167" t="n">
-        <v>0.4371</v>
+        <v>0.2202</v>
       </c>
     </row>
     <row r="168">
@@ -7762,40 +8187,40 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.9958</v>
+        <v>0.9596</v>
       </c>
       <c r="C168" t="n">
-        <v>1.0622</v>
+        <v>0.9081</v>
       </c>
       <c r="D168" t="n">
-        <v>1.1229</v>
+        <v>0.9293</v>
       </c>
       <c r="E168" t="n">
-        <v>1.0177</v>
+        <v>0.8599</v>
       </c>
       <c r="F168" t="n">
-        <v>0.9005</v>
+        <v>0.9146</v>
       </c>
       <c r="G168" t="n">
-        <v>1.1005</v>
+        <v>0.9928</v>
       </c>
       <c r="H168" t="n">
-        <v>1.0117</v>
+        <v>0.9157</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9108000000000001</v>
+        <v>1.0311</v>
       </c>
       <c r="J168" t="n">
-        <v>0.9493</v>
+        <v>0.8985</v>
       </c>
       <c r="K168" t="n">
-        <v>0.9196</v>
+        <v>0.9413</v>
       </c>
       <c r="L168" t="n">
-        <v>0.9991</v>
+        <v>0.9351</v>
       </c>
       <c r="M168" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="169">
@@ -7805,40 +8230,40 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.8633</v>
+        <v>1.2895</v>
       </c>
       <c r="C169" t="n">
-        <v>1.2112</v>
+        <v>1.0583</v>
       </c>
       <c r="D169" t="n">
-        <v>0.828</v>
+        <v>0.9463</v>
       </c>
       <c r="E169" t="n">
-        <v>1.0033</v>
+        <v>1.0433</v>
       </c>
       <c r="F169" t="n">
-        <v>0.9360000000000001</v>
+        <v>1.0718</v>
       </c>
       <c r="G169" t="n">
-        <v>0.7914</v>
+        <v>0.9819</v>
       </c>
       <c r="H169" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.9151</v>
       </c>
       <c r="I169" t="n">
-        <v>1.0556</v>
+        <v>0.9679</v>
       </c>
       <c r="J169" t="n">
-        <v>0.9972</v>
+        <v>0.9367</v>
       </c>
       <c r="K169" t="n">
-        <v>0.8665</v>
+        <v>0.92</v>
       </c>
       <c r="L169" t="n">
-        <v>0.9273</v>
+        <v>1.0131</v>
       </c>
       <c r="M169" t="n">
-        <v>0.1441</v>
+        <v>0.1127</v>
       </c>
     </row>
     <row r="170">
@@ -7848,46 +8273,46 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.9367</v>
+        <v>1.1468</v>
       </c>
       <c r="C170" t="n">
-        <v>0.8925999999999999</v>
+        <v>1.0527</v>
       </c>
       <c r="D170" t="n">
-        <v>0.9834000000000001</v>
+        <v>1.2389</v>
       </c>
       <c r="E170" t="n">
-        <v>1.0449</v>
+        <v>1.2174</v>
       </c>
       <c r="F170" t="n">
-        <v>1.059</v>
+        <v>1.2495</v>
       </c>
       <c r="G170" t="n">
-        <v>1.1741</v>
+        <v>1.2287</v>
       </c>
       <c r="H170" t="n">
-        <v>0.9233</v>
+        <v>1.318</v>
       </c>
       <c r="I170" t="n">
-        <v>0.9927</v>
+        <v>1.2425</v>
       </c>
       <c r="J170" t="n">
-        <v>1.0166</v>
+        <v>1.1517</v>
       </c>
       <c r="K170" t="n">
-        <v>0.8576</v>
+        <v>1.139</v>
       </c>
       <c r="L170" t="n">
-        <v>0.9881</v>
+        <v>1.1985</v>
       </c>
       <c r="M170" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0756</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>augmented — RMSSE</t>
+          <t>SPCP — RMSSE</t>
         </is>
       </c>
     </row>
@@ -7965,40 +8390,40 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.3284</v>
+        <v>0.3442</v>
       </c>
       <c r="C174" t="n">
-        <v>0.3618</v>
+        <v>0.3082</v>
       </c>
       <c r="D174" t="n">
-        <v>0.3332</v>
+        <v>0.3129</v>
       </c>
       <c r="E174" t="n">
-        <v>0.3978</v>
+        <v>0.3347</v>
       </c>
       <c r="F174" t="n">
-        <v>0.4483</v>
+        <v>0.3614</v>
       </c>
       <c r="G174" t="n">
-        <v>0.3452</v>
+        <v>0.3302</v>
       </c>
       <c r="H174" t="n">
-        <v>0.4018</v>
+        <v>0.3697</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3913</v>
+        <v>0.3801</v>
       </c>
       <c r="J174" t="n">
-        <v>0.5659</v>
+        <v>0.3408</v>
       </c>
       <c r="K174" t="n">
-        <v>0.2963</v>
+        <v>0.3714</v>
       </c>
       <c r="L174" t="n">
-        <v>0.387</v>
+        <v>0.3454</v>
       </c>
       <c r="M174" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0248</v>
       </c>
     </row>
     <row r="175">
@@ -8008,40 +8433,40 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.9453</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="C175" t="n">
-        <v>1.1324</v>
+        <v>0.9583</v>
       </c>
       <c r="D175" t="n">
-        <v>0.9812</v>
+        <v>0.9634</v>
       </c>
       <c r="E175" t="n">
-        <v>1.0021</v>
+        <v>1.0169</v>
       </c>
       <c r="F175" t="n">
-        <v>1.0055</v>
+        <v>1.0791</v>
       </c>
       <c r="G175" t="n">
-        <v>1.073</v>
+        <v>1.0206</v>
       </c>
       <c r="H175" t="n">
-        <v>0.9436</v>
+        <v>1.0911</v>
       </c>
       <c r="I175" t="n">
-        <v>0.9253</v>
+        <v>0.9948</v>
       </c>
       <c r="J175" t="n">
-        <v>1.0482</v>
+        <v>1.0437</v>
       </c>
       <c r="K175" t="n">
-        <v>0.9242</v>
+        <v>1.0483</v>
       </c>
       <c r="L175" t="n">
-        <v>0.9981</v>
+        <v>1.0189</v>
       </c>
       <c r="M175" t="n">
-        <v>0.0692</v>
+        <v>0.0468</v>
       </c>
     </row>
     <row r="176">
@@ -8051,40 +8476,40 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.4771</v>
+        <v>0.6444</v>
       </c>
       <c r="C176" t="n">
-        <v>0.406</v>
+        <v>0.7062</v>
       </c>
       <c r="D176" t="n">
-        <v>0.4189</v>
+        <v>0.5219</v>
       </c>
       <c r="E176" t="n">
-        <v>0.4357</v>
+        <v>0.7763</v>
       </c>
       <c r="F176" t="n">
-        <v>0.3945</v>
+        <v>0.6047</v>
       </c>
       <c r="G176" t="n">
-        <v>0.5386</v>
+        <v>0.4674</v>
       </c>
       <c r="H176" t="n">
-        <v>0.5392</v>
+        <v>0.6099</v>
       </c>
       <c r="I176" t="n">
-        <v>0.5215</v>
+        <v>0.6029</v>
       </c>
       <c r="J176" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5154</v>
       </c>
       <c r="K176" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.613</v>
       </c>
       <c r="L176" t="n">
-        <v>0.4883</v>
+        <v>0.6062</v>
       </c>
       <c r="M176" t="n">
-        <v>0.0706</v>
+        <v>0.09130000000000001</v>
       </c>
     </row>
     <row r="177">
@@ -8094,40 +8519,40 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1.2639</v>
+        <v>0.9216</v>
       </c>
       <c r="C177" t="n">
-        <v>0.9726</v>
+        <v>0.8917</v>
       </c>
       <c r="D177" t="n">
-        <v>1.0978</v>
+        <v>0.995</v>
       </c>
       <c r="E177" t="n">
-        <v>0.9608</v>
+        <v>0.947</v>
       </c>
       <c r="F177" t="n">
-        <v>1.031</v>
+        <v>0.9547</v>
       </c>
       <c r="G177" t="n">
-        <v>0.9519</v>
+        <v>0.8595</v>
       </c>
       <c r="H177" t="n">
-        <v>0.9326</v>
+        <v>1.0603</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9026</v>
+        <v>1.0107</v>
       </c>
       <c r="J177" t="n">
-        <v>0.9426</v>
+        <v>1.0559</v>
       </c>
       <c r="K177" t="n">
-        <v>1.0107</v>
+        <v>0.9438</v>
       </c>
       <c r="L177" t="n">
-        <v>1.0067</v>
+        <v>0.964</v>
       </c>
       <c r="M177" t="n">
-        <v>0.1063</v>
+        <v>0.0663</v>
       </c>
     </row>
     <row r="178">
@@ -8137,40 +8562,40 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>1.0608</v>
+        <v>1.467</v>
       </c>
       <c r="C178" t="n">
-        <v>1.2428</v>
+        <v>0.9235</v>
       </c>
       <c r="D178" t="n">
-        <v>1.2041</v>
+        <v>1.2671</v>
       </c>
       <c r="E178" t="n">
-        <v>1.0041</v>
+        <v>1.0446</v>
       </c>
       <c r="F178" t="n">
-        <v>1.2589</v>
+        <v>1.2183</v>
       </c>
       <c r="G178" t="n">
-        <v>0.8979</v>
+        <v>0.9852</v>
       </c>
       <c r="H178" t="n">
-        <v>0.8208</v>
+        <v>1.0584</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9836</v>
+        <v>1.2636</v>
       </c>
       <c r="J178" t="n">
-        <v>0.8174</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="K178" t="n">
-        <v>0.8495</v>
+        <v>0.962</v>
       </c>
       <c r="L178" t="n">
-        <v>1.014</v>
+        <v>1.1105</v>
       </c>
       <c r="M178" t="n">
-        <v>0.1726</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="179">
@@ -8180,40 +8605,40 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.5236</v>
+        <v>0.5299</v>
       </c>
       <c r="C179" t="n">
-        <v>0.4763</v>
+        <v>0.5052</v>
       </c>
       <c r="D179" t="n">
-        <v>0.4722</v>
+        <v>0.4981</v>
       </c>
       <c r="E179" t="n">
-        <v>0.5014</v>
+        <v>0.481</v>
       </c>
       <c r="F179" t="n">
-        <v>0.5139</v>
+        <v>0.5364</v>
       </c>
       <c r="G179" t="n">
-        <v>0.4782</v>
+        <v>0.5099</v>
       </c>
       <c r="H179" t="n">
-        <v>0.5028</v>
+        <v>0.5122</v>
       </c>
       <c r="I179" t="n">
-        <v>0.5178</v>
+        <v>0.5098</v>
       </c>
       <c r="J179" t="n">
-        <v>0.4918</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="K179" t="n">
-        <v>0.5475</v>
+        <v>0.5369</v>
       </c>
       <c r="L179" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.5122</v>
       </c>
       <c r="M179" t="n">
-        <v>0.0239</v>
+        <v>0.0178</v>
       </c>
     </row>
     <row r="180">
@@ -8223,40 +8648,40 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.984</v>
+        <v>0.8555</v>
       </c>
       <c r="C180" t="n">
-        <v>1.2256</v>
+        <v>0.7808</v>
       </c>
       <c r="D180" t="n">
-        <v>0.805</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="E180" t="n">
-        <v>0.8119</v>
+        <v>0.8595</v>
       </c>
       <c r="F180" t="n">
-        <v>1.2238</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="G180" t="n">
-        <v>1.4771</v>
+        <v>0.9885</v>
       </c>
       <c r="H180" t="n">
-        <v>1.2054</v>
+        <v>0.8713</v>
       </c>
       <c r="I180" t="n">
-        <v>1.0834</v>
+        <v>0.7964</v>
       </c>
       <c r="J180" t="n">
-        <v>1.4375</v>
+        <v>1.0671</v>
       </c>
       <c r="K180" t="n">
-        <v>0.8208</v>
+        <v>0.7365</v>
       </c>
       <c r="L180" t="n">
-        <v>1.1074</v>
+        <v>0.8701</v>
       </c>
       <c r="M180" t="n">
-        <v>0.2493</v>
+        <v>0.0994</v>
       </c>
     </row>
     <row r="181">
@@ -8266,40 +8691,40 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>1.0018</v>
+        <v>1.0274</v>
       </c>
       <c r="C181" t="n">
-        <v>0.9984</v>
+        <v>0.9061</v>
       </c>
       <c r="D181" t="n">
-        <v>1.0023</v>
+        <v>0.996</v>
       </c>
       <c r="E181" t="n">
-        <v>0.9378</v>
+        <v>0.9872</v>
       </c>
       <c r="F181" t="n">
-        <v>0.946</v>
+        <v>1.0295</v>
       </c>
       <c r="G181" t="n">
-        <v>1.0394</v>
+        <v>0.9957</v>
       </c>
       <c r="H181" t="n">
-        <v>1.0059</v>
+        <v>0.9502</v>
       </c>
       <c r="I181" t="n">
-        <v>0.9971</v>
+        <v>1.0216</v>
       </c>
       <c r="J181" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9647</v>
       </c>
       <c r="K181" t="n">
-        <v>0.9111</v>
+        <v>1.0005</v>
       </c>
       <c r="L181" t="n">
-        <v>0.9776</v>
+        <v>0.9879</v>
       </c>
       <c r="M181" t="n">
-        <v>0.0413</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="182">
@@ -8309,40 +8734,40 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.6546</v>
+        <v>1.0812</v>
       </c>
       <c r="C182" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.875</v>
       </c>
       <c r="D182" t="n">
-        <v>0.6222</v>
+        <v>0.8288</v>
       </c>
       <c r="E182" t="n">
-        <v>0.821</v>
+        <v>0.8582</v>
       </c>
       <c r="F182" t="n">
-        <v>0.7524999999999999</v>
+        <v>1.0164</v>
       </c>
       <c r="G182" t="n">
-        <v>0.6262</v>
+        <v>0.7489</v>
       </c>
       <c r="H182" t="n">
-        <v>0.6183</v>
+        <v>0.7275</v>
       </c>
       <c r="I182" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.754</v>
       </c>
       <c r="J182" t="n">
-        <v>0.7459</v>
+        <v>0.7748</v>
       </c>
       <c r="K182" t="n">
-        <v>0.7208</v>
+        <v>0.7431</v>
       </c>
       <c r="L182" t="n">
-        <v>0.7299</v>
+        <v>0.8408</v>
       </c>
       <c r="M182" t="n">
-        <v>0.1054</v>
+        <v>0.1216</v>
       </c>
     </row>
     <row r="183">
@@ -8352,46 +8777,46 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.9516</v>
       </c>
       <c r="C183" t="n">
-        <v>0.853</v>
+        <v>0.9006</v>
       </c>
       <c r="D183" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.9957</v>
       </c>
       <c r="E183" t="n">
-        <v>0.8975</v>
+        <v>0.994</v>
       </c>
       <c r="F183" t="n">
-        <v>0.9189000000000001</v>
+        <v>1.0321</v>
       </c>
       <c r="G183" t="n">
-        <v>0.899</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H183" t="n">
-        <v>0.8843</v>
+        <v>1.0204</v>
       </c>
       <c r="I183" t="n">
-        <v>0.8786</v>
+        <v>1.0156</v>
       </c>
       <c r="J183" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.9254</v>
       </c>
       <c r="K183" t="n">
-        <v>0.8729</v>
+        <v>0.9547</v>
       </c>
       <c r="L183" t="n">
-        <v>0.8777</v>
+        <v>0.9731</v>
       </c>
       <c r="M183" t="n">
-        <v>0.0264</v>
+        <v>0.0445</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>r+r — MASE</t>
+          <t>augmented — MASE</t>
         </is>
       </c>
     </row>
@@ -8469,40 +8894,40 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.5471</v>
+        <v>0.4529</v>
       </c>
       <c r="C187" t="n">
-        <v>0.4441</v>
+        <v>0.3958</v>
       </c>
       <c r="D187" t="n">
-        <v>0.4946</v>
+        <v>0.4034</v>
       </c>
       <c r="E187" t="n">
-        <v>0.5386</v>
+        <v>0.5661</v>
       </c>
       <c r="F187" t="n">
-        <v>0.5113</v>
+        <v>0.4994</v>
       </c>
       <c r="G187" t="n">
-        <v>0.3209</v>
+        <v>0.4695</v>
       </c>
       <c r="H187" t="n">
-        <v>0.5653</v>
+        <v>0.369</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4039</v>
+        <v>0.6643</v>
       </c>
       <c r="J187" t="n">
-        <v>0.4821</v>
+        <v>0.7598</v>
       </c>
       <c r="K187" t="n">
-        <v>0.3611</v>
+        <v>0.5317</v>
       </c>
       <c r="L187" t="n">
-        <v>0.4669</v>
+        <v>0.5112</v>
       </c>
       <c r="M187" t="n">
-        <v>0.0825</v>
+        <v>0.1243</v>
       </c>
     </row>
     <row r="188">
@@ -8512,40 +8937,40 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1.0655</v>
+        <v>1.293</v>
       </c>
       <c r="C188" t="n">
-        <v>1.0894</v>
+        <v>0.9578</v>
       </c>
       <c r="D188" t="n">
-        <v>1.1019</v>
+        <v>1.0596</v>
       </c>
       <c r="E188" t="n">
-        <v>1.0125</v>
+        <v>1.0416</v>
       </c>
       <c r="F188" t="n">
-        <v>1.0181</v>
+        <v>1.3011</v>
       </c>
       <c r="G188" t="n">
-        <v>1.1197</v>
+        <v>1.2881</v>
       </c>
       <c r="H188" t="n">
-        <v>1.0427</v>
+        <v>1.0459</v>
       </c>
       <c r="I188" t="n">
-        <v>1.3079</v>
+        <v>1.0511</v>
       </c>
       <c r="J188" t="n">
-        <v>1.1108</v>
+        <v>0.9882</v>
       </c>
       <c r="K188" t="n">
-        <v>0.8869</v>
+        <v>1.0326</v>
       </c>
       <c r="L188" t="n">
-        <v>1.0755</v>
+        <v>1.1059</v>
       </c>
       <c r="M188" t="n">
-        <v>0.1065</v>
+        <v>0.1335</v>
       </c>
     </row>
     <row r="189">
@@ -8555,40 +8980,40 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.624</v>
+        <v>0.8428</v>
       </c>
       <c r="C189" t="n">
-        <v>1.4071</v>
+        <v>1.0307</v>
       </c>
       <c r="D189" t="n">
-        <v>0.9873</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="E189" t="n">
-        <v>0.8855</v>
+        <v>0.6707</v>
       </c>
       <c r="F189" t="n">
-        <v>1.1475</v>
+        <v>0.5886</v>
       </c>
       <c r="G189" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.7116</v>
       </c>
       <c r="H189" t="n">
-        <v>0.6511</v>
+        <v>0.6795</v>
       </c>
       <c r="I189" t="n">
-        <v>0.7582</v>
+        <v>0.7493</v>
       </c>
       <c r="J189" t="n">
-        <v>0.8704</v>
+        <v>0.8541</v>
       </c>
       <c r="K189" t="n">
-        <v>0.9579</v>
+        <v>0.8272</v>
       </c>
       <c r="L189" t="n">
-        <v>0.8917</v>
+        <v>0.7513</v>
       </c>
       <c r="M189" t="n">
-        <v>0.2498</v>
+        <v>0.1412</v>
       </c>
     </row>
     <row r="190">
@@ -8598,40 +9023,40 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>1.0446</v>
+        <v>0.9626</v>
       </c>
       <c r="C190" t="n">
-        <v>1.0842</v>
+        <v>0.9848</v>
       </c>
       <c r="D190" t="n">
-        <v>1.0628</v>
+        <v>1.1048</v>
       </c>
       <c r="E190" t="n">
-        <v>1.0112</v>
+        <v>1.159</v>
       </c>
       <c r="F190" t="n">
-        <v>1.0428</v>
+        <v>1.3324</v>
       </c>
       <c r="G190" t="n">
-        <v>1.0199</v>
+        <v>0.997</v>
       </c>
       <c r="H190" t="n">
-        <v>1.0391</v>
+        <v>1.0469</v>
       </c>
       <c r="I190" t="n">
-        <v>0.9464</v>
+        <v>0.9755</v>
       </c>
       <c r="J190" t="n">
-        <v>1.2436</v>
+        <v>1.288</v>
       </c>
       <c r="K190" t="n">
-        <v>1.0514</v>
+        <v>1.1363</v>
       </c>
       <c r="L190" t="n">
-        <v>1.0546</v>
+        <v>1.0987</v>
       </c>
       <c r="M190" t="n">
-        <v>0.076</v>
+        <v>0.1314</v>
       </c>
     </row>
     <row r="191">
@@ -8641,40 +9066,40 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>1.0445</v>
+        <v>1.6353</v>
       </c>
       <c r="C191" t="n">
-        <v>1.2796</v>
+        <v>1.3345</v>
       </c>
       <c r="D191" t="n">
-        <v>1.0702</v>
+        <v>0.9892</v>
       </c>
       <c r="E191" t="n">
-        <v>1.3081</v>
+        <v>1.4212</v>
       </c>
       <c r="F191" t="n">
-        <v>1.6489</v>
+        <v>1.8169</v>
       </c>
       <c r="G191" t="n">
-        <v>1.2336</v>
+        <v>1.449</v>
       </c>
       <c r="H191" t="n">
-        <v>1.0771</v>
+        <v>1.7369</v>
       </c>
       <c r="I191" t="n">
-        <v>1.1196</v>
+        <v>1.4692</v>
       </c>
       <c r="J191" t="n">
-        <v>1.3489</v>
+        <v>1.0691</v>
       </c>
       <c r="K191" t="n">
-        <v>1.1109</v>
+        <v>1.888</v>
       </c>
       <c r="L191" t="n">
-        <v>1.2241</v>
+        <v>1.4809</v>
       </c>
       <c r="M191" t="n">
-        <v>0.1849</v>
+        <v>0.2992</v>
       </c>
     </row>
     <row r="192">
@@ -8684,40 +9109,40 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.4149</v>
+        <v>0.4329</v>
       </c>
       <c r="C192" t="n">
-        <v>0.5091</v>
+        <v>0.4926</v>
       </c>
       <c r="D192" t="n">
-        <v>0.4132</v>
+        <v>0.4978</v>
       </c>
       <c r="E192" t="n">
-        <v>0.331</v>
+        <v>0.3583</v>
       </c>
       <c r="F192" t="n">
-        <v>0.4339</v>
+        <v>0.4412</v>
       </c>
       <c r="G192" t="n">
-        <v>0.4071</v>
+        <v>0.4759</v>
       </c>
       <c r="H192" t="n">
-        <v>0.4259</v>
+        <v>0.4955</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4118</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="J192" t="n">
-        <v>0.4485</v>
+        <v>0.4696</v>
       </c>
       <c r="K192" t="n">
-        <v>0.4357</v>
+        <v>0.4559</v>
       </c>
       <c r="L192" t="n">
-        <v>0.4231</v>
+        <v>0.4626</v>
       </c>
       <c r="M192" t="n">
-        <v>0.0439</v>
+        <v>0.0443</v>
       </c>
     </row>
     <row r="193">
@@ -8727,40 +9152,40 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>1.4881</v>
+        <v>1.3817</v>
       </c>
       <c r="C193" t="n">
-        <v>1.4027</v>
+        <v>1.1626</v>
       </c>
       <c r="D193" t="n">
-        <v>1.4771</v>
+        <v>1.1408</v>
       </c>
       <c r="E193" t="n">
-        <v>1.0101</v>
+        <v>1.0405</v>
       </c>
       <c r="F193" t="n">
-        <v>1.5876</v>
+        <v>1.3917</v>
       </c>
       <c r="G193" t="n">
-        <v>1.2691</v>
+        <v>1.4982</v>
       </c>
       <c r="H193" t="n">
-        <v>1.4235</v>
+        <v>1.3354</v>
       </c>
       <c r="I193" t="n">
-        <v>1.4386</v>
+        <v>1.2883</v>
       </c>
       <c r="J193" t="n">
-        <v>1.3941</v>
+        <v>1.4201</v>
       </c>
       <c r="K193" t="n">
-        <v>1.2545</v>
+        <v>1.3094</v>
       </c>
       <c r="L193" t="n">
-        <v>1.3745</v>
+        <v>1.2969</v>
       </c>
       <c r="M193" t="n">
-        <v>0.1615</v>
+        <v>0.1421</v>
       </c>
     </row>
     <row r="194">
@@ -8770,40 +9195,40 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>1.0236</v>
+        <v>1.0755</v>
       </c>
       <c r="C194" t="n">
-        <v>1.225</v>
+        <v>0.9022</v>
       </c>
       <c r="D194" t="n">
-        <v>1.0572</v>
+        <v>0.9493</v>
       </c>
       <c r="E194" t="n">
-        <v>1.0222</v>
+        <v>0.9992</v>
       </c>
       <c r="F194" t="n">
-        <v>1.0695</v>
+        <v>1.0219</v>
       </c>
       <c r="G194" t="n">
-        <v>1.0399</v>
+        <v>1.0021</v>
       </c>
       <c r="H194" t="n">
-        <v>0.9366</v>
+        <v>0.9958</v>
       </c>
       <c r="I194" t="n">
-        <v>1.1201</v>
+        <v>1.0462</v>
       </c>
       <c r="J194" t="n">
-        <v>0.9862</v>
+        <v>1.0099</v>
       </c>
       <c r="K194" t="n">
-        <v>1.0589</v>
+        <v>1.0327</v>
       </c>
       <c r="L194" t="n">
-        <v>1.0539</v>
+        <v>1.0035</v>
       </c>
       <c r="M194" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0489</v>
       </c>
     </row>
     <row r="195">
@@ -8813,40 +9238,40 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.9715</v>
+        <v>1.0688</v>
       </c>
       <c r="C195" t="n">
-        <v>1.1481</v>
+        <v>0.752</v>
       </c>
       <c r="D195" t="n">
-        <v>1.0141</v>
+        <v>1.0577</v>
       </c>
       <c r="E195" t="n">
-        <v>1.4152</v>
+        <v>1.1971</v>
       </c>
       <c r="F195" t="n">
-        <v>1.2115</v>
+        <v>1.0106</v>
       </c>
       <c r="G195" t="n">
-        <v>1.2826</v>
+        <v>0.9867</v>
       </c>
       <c r="H195" t="n">
-        <v>1.1975</v>
+        <v>0.8504</v>
       </c>
       <c r="I195" t="n">
-        <v>1.0394</v>
+        <v>1.1344</v>
       </c>
       <c r="J195" t="n">
-        <v>0.8759</v>
+        <v>0.9144</v>
       </c>
       <c r="K195" t="n">
-        <v>0.7199</v>
+        <v>0.7331</v>
       </c>
       <c r="L195" t="n">
-        <v>1.0876</v>
+        <v>0.9705</v>
       </c>
       <c r="M195" t="n">
-        <v>0.2049</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="196">
@@ -8856,46 +9281,46 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>1.0042</v>
+        <v>1.2288</v>
       </c>
       <c r="C196" t="n">
-        <v>0.9002</v>
+        <v>1.2376</v>
       </c>
       <c r="D196" t="n">
-        <v>0.9257</v>
+        <v>1.1746</v>
       </c>
       <c r="E196" t="n">
-        <v>1.1281</v>
+        <v>0.975</v>
       </c>
       <c r="F196" t="n">
-        <v>0.9978</v>
+        <v>1.0523</v>
       </c>
       <c r="G196" t="n">
-        <v>1.0812</v>
+        <v>1.0584</v>
       </c>
       <c r="H196" t="n">
-        <v>0.9673</v>
+        <v>1.0517</v>
       </c>
       <c r="I196" t="n">
-        <v>0.9965000000000001</v>
+        <v>1.2753</v>
       </c>
       <c r="J196" t="n">
-        <v>0.8994</v>
+        <v>0.9698</v>
       </c>
       <c r="K196" t="n">
-        <v>1.0284</v>
+        <v>1.0198</v>
       </c>
       <c r="L196" t="n">
-        <v>0.9929</v>
+        <v>1.1043</v>
       </c>
       <c r="M196" t="n">
-        <v>0.0745</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>r+r — RMSSE</t>
+          <t>augmented — RMSSE</t>
         </is>
       </c>
     </row>
@@ -8973,40 +9398,40 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.31</v>
+        <v>0.2892</v>
       </c>
       <c r="C200" t="n">
-        <v>0.2881</v>
+        <v>0.2642</v>
       </c>
       <c r="D200" t="n">
-        <v>0.3556</v>
+        <v>0.2808</v>
       </c>
       <c r="E200" t="n">
-        <v>0.3383</v>
+        <v>0.3559</v>
       </c>
       <c r="F200" t="n">
-        <v>0.3349</v>
+        <v>0.3134</v>
       </c>
       <c r="G200" t="n">
-        <v>0.2799</v>
+        <v>0.3177</v>
       </c>
       <c r="H200" t="n">
-        <v>0.3413</v>
+        <v>0.2664</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3032</v>
+        <v>0.3989</v>
       </c>
       <c r="J200" t="n">
-        <v>0.31</v>
+        <v>0.4717</v>
       </c>
       <c r="K200" t="n">
-        <v>0.2685</v>
+        <v>0.3681</v>
       </c>
       <c r="L200" t="n">
-        <v>0.313</v>
+        <v>0.3326</v>
       </c>
       <c r="M200" t="n">
-        <v>0.0289</v>
+        <v>0.0665</v>
       </c>
     </row>
     <row r="201">
@@ -9016,40 +9441,40 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>1.0381</v>
+        <v>1.1324</v>
       </c>
       <c r="C201" t="n">
-        <v>1.0461</v>
+        <v>0.9402</v>
       </c>
       <c r="D201" t="n">
-        <v>0.9762999999999999</v>
+        <v>1.0292</v>
       </c>
       <c r="E201" t="n">
-        <v>0.9069</v>
+        <v>0.9482</v>
       </c>
       <c r="F201" t="n">
-        <v>1.0091</v>
+        <v>1.0415</v>
       </c>
       <c r="G201" t="n">
-        <v>1.0287</v>
+        <v>1.033</v>
       </c>
       <c r="H201" t="n">
-        <v>0.985</v>
+        <v>0.9552</v>
       </c>
       <c r="I201" t="n">
-        <v>1.093</v>
+        <v>0.9469</v>
       </c>
       <c r="J201" t="n">
-        <v>1.0027</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="K201" t="n">
-        <v>0.9381</v>
+        <v>1.04</v>
       </c>
       <c r="L201" t="n">
-        <v>1.0024</v>
+        <v>0.9972</v>
       </c>
       <c r="M201" t="n">
-        <v>0.0541</v>
+        <v>0.0689</v>
       </c>
     </row>
     <row r="202">
@@ -9059,40 +9484,40 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.3914</v>
+        <v>0.5154</v>
       </c>
       <c r="C202" t="n">
-        <v>0.8061</v>
+        <v>0.6075</v>
       </c>
       <c r="D202" t="n">
-        <v>0.6688</v>
+        <v>0.4043</v>
       </c>
       <c r="E202" t="n">
-        <v>0.5354</v>
+        <v>0.4443</v>
       </c>
       <c r="F202" t="n">
-        <v>0.7034</v>
+        <v>0.4058</v>
       </c>
       <c r="G202" t="n">
-        <v>0.4061</v>
+        <v>0.4735</v>
       </c>
       <c r="H202" t="n">
-        <v>0.4146</v>
+        <v>0.4405</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4819</v>
+        <v>0.4892</v>
       </c>
       <c r="J202" t="n">
-        <v>0.5245</v>
+        <v>0.5394</v>
       </c>
       <c r="K202" t="n">
-        <v>0.5688</v>
+        <v>0.5848</v>
       </c>
       <c r="L202" t="n">
-        <v>0.5501</v>
+        <v>0.4905</v>
       </c>
       <c r="M202" t="n">
-        <v>0.1388</v>
+        <v>0.0708</v>
       </c>
     </row>
     <row r="203">
@@ -9102,40 +9527,40 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.972</v>
+        <v>0.9265</v>
       </c>
       <c r="C203" t="n">
-        <v>0.9103</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="D203" t="n">
-        <v>0.9528</v>
+        <v>0.957</v>
       </c>
       <c r="E203" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.9613</v>
       </c>
       <c r="F203" t="n">
-        <v>0.9540999999999999</v>
+        <v>1.0645</v>
       </c>
       <c r="G203" t="n">
-        <v>0.8929</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="H203" t="n">
-        <v>0.854</v>
+        <v>0.9617</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9356</v>
+        <v>0.918</v>
       </c>
       <c r="J203" t="n">
-        <v>1.0836</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="K203" t="n">
-        <v>0.9475</v>
+        <v>0.9797</v>
       </c>
       <c r="L203" t="n">
-        <v>0.9433</v>
+        <v>0.9586</v>
       </c>
       <c r="M203" t="n">
-        <v>0.0602</v>
+        <v>0.0617</v>
       </c>
     </row>
     <row r="204">
@@ -9145,40 +9570,40 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.8584000000000001</v>
+        <v>1.3765</v>
       </c>
       <c r="C204" t="n">
-        <v>0.9836</v>
+        <v>1.1724</v>
       </c>
       <c r="D204" t="n">
-        <v>0.9162</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="E204" t="n">
-        <v>1.0466</v>
+        <v>1.1029</v>
       </c>
       <c r="F204" t="n">
-        <v>1.3496</v>
+        <v>1.3915</v>
       </c>
       <c r="G204" t="n">
-        <v>1.0254</v>
+        <v>1.0998</v>
       </c>
       <c r="H204" t="n">
-        <v>0.9462</v>
+        <v>1.3231</v>
       </c>
       <c r="I204" t="n">
-        <v>0.8943</v>
+        <v>1.1743</v>
       </c>
       <c r="J204" t="n">
-        <v>1.1552</v>
+        <v>0.8598</v>
       </c>
       <c r="K204" t="n">
-        <v>0.9493</v>
+        <v>1.5152</v>
       </c>
       <c r="L204" t="n">
-        <v>1.0125</v>
+        <v>1.1934</v>
       </c>
       <c r="M204" t="n">
-        <v>0.1459</v>
+        <v>0.2102</v>
       </c>
     </row>
     <row r="205">
@@ -9188,40 +9613,40 @@
         </is>
       </c>
       <c r="B205" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0.5124</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="E205" t="n">
         <v>0.4711</v>
       </c>
-      <c r="C205" t="n">
-        <v>0.4782</v>
-      </c>
-      <c r="D205" t="n">
-        <v>0.4702</v>
-      </c>
-      <c r="E205" t="n">
-        <v>0.4441</v>
-      </c>
       <c r="F205" t="n">
-        <v>0.4675</v>
+        <v>0.4779</v>
       </c>
       <c r="G205" t="n">
-        <v>0.4873</v>
+        <v>0.5043</v>
       </c>
       <c r="H205" t="n">
-        <v>0.4856</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4516</v>
+        <v>0.5177</v>
       </c>
       <c r="J205" t="n">
-        <v>0.5</v>
+        <v>0.4973</v>
       </c>
       <c r="K205" t="n">
-        <v>0.4795</v>
+        <v>0.508</v>
       </c>
       <c r="L205" t="n">
-        <v>0.4735</v>
+        <v>0.4991</v>
       </c>
       <c r="M205" t="n">
-        <v>0.0167</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="206">
@@ -9231,40 +9656,40 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>1.0342</v>
+        <v>0.8757</v>
       </c>
       <c r="C206" t="n">
-        <v>0.9638</v>
+        <v>0.9129</v>
       </c>
       <c r="D206" t="n">
-        <v>0.9867</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E206" t="n">
-        <v>0.7519</v>
+        <v>0.7346</v>
       </c>
       <c r="F206" t="n">
-        <v>0.9343</v>
+        <v>0.8636</v>
       </c>
       <c r="G206" t="n">
-        <v>0.8274</v>
+        <v>1.009</v>
       </c>
       <c r="H206" t="n">
-        <v>0.9437</v>
+        <v>0.8253</v>
       </c>
       <c r="I206" t="n">
-        <v>0.9831</v>
+        <v>0.9042</v>
       </c>
       <c r="J206" t="n">
-        <v>0.8935</v>
+        <v>0.8937</v>
       </c>
       <c r="K206" t="n">
-        <v>0.8624000000000001</v>
+        <v>0.9204</v>
       </c>
       <c r="L206" t="n">
-        <v>0.9181</v>
+        <v>0.8754</v>
       </c>
       <c r="M206" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0735</v>
       </c>
     </row>
     <row r="207">
@@ -9274,40 +9699,40 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>1.053</v>
+        <v>1.034</v>
       </c>
       <c r="C207" t="n">
-        <v>1.0436</v>
+        <v>0.9477</v>
       </c>
       <c r="D207" t="n">
-        <v>1.0474</v>
+        <v>0.9513</v>
       </c>
       <c r="E207" t="n">
-        <v>1.0296</v>
+        <v>1.0725</v>
       </c>
       <c r="F207" t="n">
-        <v>1.0206</v>
+        <v>1.0718</v>
       </c>
       <c r="G207" t="n">
-        <v>1.031</v>
+        <v>1.017</v>
       </c>
       <c r="H207" t="n">
-        <v>1.0034</v>
+        <v>1.0076</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0806</v>
+        <v>1.0628</v>
       </c>
       <c r="J207" t="n">
-        <v>0.9697</v>
+        <v>1.0063</v>
       </c>
       <c r="K207" t="n">
-        <v>1.0116</v>
+        <v>1.0299</v>
       </c>
       <c r="L207" t="n">
-        <v>1.029</v>
+        <v>1.0201</v>
       </c>
       <c r="M207" t="n">
-        <v>0.0304</v>
+        <v>0.0445</v>
       </c>
     </row>
     <row r="208">
@@ -9317,40 +9742,40 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.8137</v>
+        <v>0.8237</v>
       </c>
       <c r="C208" t="n">
-        <v>0.8693</v>
+        <v>0.5752</v>
       </c>
       <c r="D208" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.791</v>
       </c>
       <c r="E208" t="n">
-        <v>1.1013</v>
+        <v>0.9712</v>
       </c>
       <c r="F208" t="n">
-        <v>0.9167</v>
+        <v>0.7806</v>
       </c>
       <c r="G208" t="n">
-        <v>1.0612</v>
+        <v>0.7214</v>
       </c>
       <c r="H208" t="n">
-        <v>0.9303</v>
+        <v>0.7127</v>
       </c>
       <c r="I208" t="n">
-        <v>0.788</v>
+        <v>0.8758</v>
       </c>
       <c r="J208" t="n">
-        <v>0.7007</v>
+        <v>0.6644</v>
       </c>
       <c r="K208" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5884</v>
       </c>
       <c r="L208" t="n">
-        <v>0.8626</v>
+        <v>0.7504</v>
       </c>
       <c r="M208" t="n">
-        <v>0.1554</v>
+        <v>0.1243</v>
       </c>
     </row>
     <row r="209">
@@ -9360,39 +9785,1047 @@
         </is>
       </c>
       <c r="B209" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.9749</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.9697</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0.8954</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0.8764999999999999</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0.9413</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0.9643</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0.8947000000000001</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0.9107</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0.0388</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>r+r — MASE</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>household</t>
+        </is>
+      </c>
+      <c r="B212" s="1" t="inlineStr">
+        <is>
+          <t>seed0</t>
+        </is>
+      </c>
+      <c r="C212" s="1" t="inlineStr">
+        <is>
+          <t>seed1</t>
+        </is>
+      </c>
+      <c r="D212" s="1" t="inlineStr">
+        <is>
+          <t>seed2</t>
+        </is>
+      </c>
+      <c r="E212" s="1" t="inlineStr">
+        <is>
+          <t>seed3</t>
+        </is>
+      </c>
+      <c r="F212" s="1" t="inlineStr">
+        <is>
+          <t>seed4</t>
+        </is>
+      </c>
+      <c r="G212" s="1" t="inlineStr">
+        <is>
+          <t>seed5</t>
+        </is>
+      </c>
+      <c r="H212" s="1" t="inlineStr">
+        <is>
+          <t>seed6</t>
+        </is>
+      </c>
+      <c r="I212" s="1" t="inlineStr">
+        <is>
+          <t>seed7</t>
+        </is>
+      </c>
+      <c r="J212" s="1" t="inlineStr">
+        <is>
+          <t>seed8</t>
+        </is>
+      </c>
+      <c r="K212" s="1" t="inlineStr">
+        <is>
+          <t>seed9</t>
+        </is>
+      </c>
+      <c r="L212" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="M212" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>building11</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>0.5471</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0.4441</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0.5386</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0.5113</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0.5653</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0.4039</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0.4821</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0.4669</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0.0825</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>building13</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1.0655</v>
+      </c>
+      <c r="C214" t="n">
+        <v>1.0894</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1.1019</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1.0125</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1.0181</v>
+      </c>
+      <c r="G214" t="n">
+        <v>1.1197</v>
+      </c>
+      <c r="H214" t="n">
+        <v>1.0427</v>
+      </c>
+      <c r="I214" t="n">
+        <v>1.3079</v>
+      </c>
+      <c r="J214" t="n">
+        <v>1.1108</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0.8869</v>
+      </c>
+      <c r="L214" t="n">
+        <v>1.0755</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0.1065</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>building17</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1.4071</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.9873</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0.8855</v>
+      </c>
+      <c r="F215" t="n">
+        <v>1.1475</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0.6284999999999999</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0.6511</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0.7582</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0.8704</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0.9579</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0.8917</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0.2498</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>building19</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>1.0446</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1.0842</v>
+      </c>
+      <c r="D216" t="n">
+        <v>1.0628</v>
+      </c>
+      <c r="E216" t="n">
+        <v>1.0112</v>
+      </c>
+      <c r="F216" t="n">
+        <v>1.0428</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1.0199</v>
+      </c>
+      <c r="H216" t="n">
+        <v>1.0391</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0.9464</v>
+      </c>
+      <c r="J216" t="n">
+        <v>1.2436</v>
+      </c>
+      <c r="K216" t="n">
+        <v>1.0514</v>
+      </c>
+      <c r="L216" t="n">
+        <v>1.0546</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0.076</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>building20</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1.0445</v>
+      </c>
+      <c r="C217" t="n">
+        <v>1.2796</v>
+      </c>
+      <c r="D217" t="n">
+        <v>1.0702</v>
+      </c>
+      <c r="E217" t="n">
+        <v>1.3081</v>
+      </c>
+      <c r="F217" t="n">
+        <v>1.6489</v>
+      </c>
+      <c r="G217" t="n">
+        <v>1.2336</v>
+      </c>
+      <c r="H217" t="n">
+        <v>1.0771</v>
+      </c>
+      <c r="I217" t="n">
+        <v>1.1196</v>
+      </c>
+      <c r="J217" t="n">
+        <v>1.3489</v>
+      </c>
+      <c r="K217" t="n">
+        <v>1.1109</v>
+      </c>
+      <c r="L217" t="n">
+        <v>1.2241</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0.1849</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>building3</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0.5091</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0.4339</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0.0439</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>building5</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1.4881</v>
+      </c>
+      <c r="C219" t="n">
+        <v>1.4027</v>
+      </c>
+      <c r="D219" t="n">
+        <v>1.4771</v>
+      </c>
+      <c r="E219" t="n">
+        <v>1.0101</v>
+      </c>
+      <c r="F219" t="n">
+        <v>1.5876</v>
+      </c>
+      <c r="G219" t="n">
+        <v>1.2691</v>
+      </c>
+      <c r="H219" t="n">
+        <v>1.4235</v>
+      </c>
+      <c r="I219" t="n">
+        <v>1.4386</v>
+      </c>
+      <c r="J219" t="n">
+        <v>1.3941</v>
+      </c>
+      <c r="K219" t="n">
+        <v>1.2545</v>
+      </c>
+      <c r="L219" t="n">
+        <v>1.3745</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0.1615</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>building6</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1.0236</v>
+      </c>
+      <c r="C220" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="D220" t="n">
+        <v>1.0572</v>
+      </c>
+      <c r="E220" t="n">
+        <v>1.0222</v>
+      </c>
+      <c r="F220" t="n">
+        <v>1.0695</v>
+      </c>
+      <c r="G220" t="n">
+        <v>1.0399</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0.9366</v>
+      </c>
+      <c r="I220" t="n">
+        <v>1.1201</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0.9862</v>
+      </c>
+      <c r="K220" t="n">
+        <v>1.0589</v>
+      </c>
+      <c r="L220" t="n">
+        <v>1.0539</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0.07770000000000001</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>building8</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>0.9715</v>
+      </c>
+      <c r="C221" t="n">
+        <v>1.1481</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1.0141</v>
+      </c>
+      <c r="E221" t="n">
+        <v>1.4152</v>
+      </c>
+      <c r="F221" t="n">
+        <v>1.2115</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1.2826</v>
+      </c>
+      <c r="H221" t="n">
+        <v>1.1975</v>
+      </c>
+      <c r="I221" t="n">
+        <v>1.0394</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0.8759</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0.7199</v>
+      </c>
+      <c r="L221" t="n">
+        <v>1.0876</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0.2049</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>building9</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1.0042</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.9002</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0.9257</v>
+      </c>
+      <c r="E222" t="n">
+        <v>1.1281</v>
+      </c>
+      <c r="F222" t="n">
+        <v>0.9978</v>
+      </c>
+      <c r="G222" t="n">
+        <v>1.0812</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0.9673</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0.9965000000000001</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0.8994</v>
+      </c>
+      <c r="K222" t="n">
+        <v>1.0284</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0.9929</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0.0745</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>r+r — RMSSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>household</t>
+        </is>
+      </c>
+      <c r="B225" s="1" t="inlineStr">
+        <is>
+          <t>seed0</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="inlineStr">
+        <is>
+          <t>seed1</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="inlineStr">
+        <is>
+          <t>seed2</t>
+        </is>
+      </c>
+      <c r="E225" s="1" t="inlineStr">
+        <is>
+          <t>seed3</t>
+        </is>
+      </c>
+      <c r="F225" s="1" t="inlineStr">
+        <is>
+          <t>seed4</t>
+        </is>
+      </c>
+      <c r="G225" s="1" t="inlineStr">
+        <is>
+          <t>seed5</t>
+        </is>
+      </c>
+      <c r="H225" s="1" t="inlineStr">
+        <is>
+          <t>seed6</t>
+        </is>
+      </c>
+      <c r="I225" s="1" t="inlineStr">
+        <is>
+          <t>seed7</t>
+        </is>
+      </c>
+      <c r="J225" s="1" t="inlineStr">
+        <is>
+          <t>seed8</t>
+        </is>
+      </c>
+      <c r="K225" s="1" t="inlineStr">
+        <is>
+          <t>seed9</t>
+        </is>
+      </c>
+      <c r="L225" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="M225" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>building11</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0.2799</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0.2685</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0.0289</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>building13</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>1.0381</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1.0461</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.9762999999999999</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0.9069</v>
+      </c>
+      <c r="F227" t="n">
+        <v>1.0091</v>
+      </c>
+      <c r="G227" t="n">
+        <v>1.0287</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="I227" t="n">
+        <v>1.093</v>
+      </c>
+      <c r="J227" t="n">
+        <v>1.0027</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0.9381</v>
+      </c>
+      <c r="L227" t="n">
+        <v>1.0024</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0.0541</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>building17</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0.8061</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.6688</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0.5354</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0.7034</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0.4819</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0.5245</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0.5688</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0.5501</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0.1388</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>building19</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.9103</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.9528</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0.9298999999999999</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0.9540999999999999</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0.8929</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0.9356</v>
+      </c>
+      <c r="J229" t="n">
+        <v>1.0836</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0.9475</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0.9433</v>
+      </c>
+      <c r="M229" t="n">
+        <v>0.0602</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>building20</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>0.8584000000000001</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.9162</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1.0466</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1.3496</v>
+      </c>
+      <c r="G230" t="n">
+        <v>1.0254</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0.9462</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0.8943</v>
+      </c>
+      <c r="J230" t="n">
+        <v>1.1552</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0.9493</v>
+      </c>
+      <c r="L230" t="n">
+        <v>1.0125</v>
+      </c>
+      <c r="M230" t="n">
+        <v>0.1459</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>building3</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>0.4711</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.4782</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.4702</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0.4441</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0.4675</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0.4873</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0.4856</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0.4795</v>
+      </c>
+      <c r="L231" t="n">
+        <v>0.4735</v>
+      </c>
+      <c r="M231" t="n">
+        <v>0.0167</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>building5</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>1.0342</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0.9638</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0.9867</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0.7519</v>
+      </c>
+      <c r="F232" t="n">
+        <v>0.9343</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0.8274</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0.9437</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0.9831</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0.8935</v>
+      </c>
+      <c r="K232" t="n">
+        <v>0.8624000000000001</v>
+      </c>
+      <c r="L232" t="n">
+        <v>0.9181</v>
+      </c>
+      <c r="M232" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>building6</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1.0436</v>
+      </c>
+      <c r="D233" t="n">
+        <v>1.0474</v>
+      </c>
+      <c r="E233" t="n">
+        <v>1.0296</v>
+      </c>
+      <c r="F233" t="n">
+        <v>1.0206</v>
+      </c>
+      <c r="G233" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="H233" t="n">
+        <v>1.0034</v>
+      </c>
+      <c r="I233" t="n">
+        <v>1.0806</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0.9697</v>
+      </c>
+      <c r="K233" t="n">
+        <v>1.0116</v>
+      </c>
+      <c r="L233" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="M233" t="n">
+        <v>0.0304</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>building8</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>0.8137</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.8693</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0.8633999999999999</v>
+      </c>
+      <c r="E234" t="n">
+        <v>1.1013</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0.9167</v>
+      </c>
+      <c r="G234" t="n">
+        <v>1.0612</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0.9303</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0.7007</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0.5810999999999999</v>
+      </c>
+      <c r="L234" t="n">
+        <v>0.8626</v>
+      </c>
+      <c r="M234" t="n">
+        <v>0.1554</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>building9</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
         <v>0.8868</v>
       </c>
-      <c r="C209" t="n">
+      <c r="C235" t="n">
         <v>0.8873</v>
       </c>
-      <c r="D209" t="n">
+      <c r="D235" t="n">
         <v>0.9142</v>
       </c>
-      <c r="E209" t="n">
+      <c r="E235" t="n">
         <v>0.8878</v>
       </c>
-      <c r="F209" t="n">
+      <c r="F235" t="n">
         <v>0.9253</v>
       </c>
-      <c r="G209" t="n">
+      <c r="G235" t="n">
         <v>0.9344</v>
       </c>
-      <c r="H209" t="n">
+      <c r="H235" t="n">
         <v>0.9</v>
       </c>
-      <c r="I209" t="n">
+      <c r="I235" t="n">
         <v>0.9325</v>
       </c>
-      <c r="J209" t="n">
+      <c r="J235" t="n">
         <v>0.8711</v>
       </c>
-      <c r="K209" t="n">
+      <c r="K235" t="n">
         <v>0.895</v>
       </c>
-      <c r="L209" t="n">
+      <c r="L235" t="n">
         <v>0.9034</v>
       </c>
-      <c r="M209" t="n">
+      <c r="M235" t="n">
         <v>0.0219</v>
       </c>
     </row>
@@ -10415,7 +11848,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>training data: synthetic (mUPC): noUPC + mapped UPC (= Ch.5 noSPCP)</t>
+          <t>training data: synthetic (mUPC): noUPC + mapped UPC</t>
         </is>
       </c>
     </row>
@@ -11055,7 +12488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>experiment: SPCP_NBEATS</t>
+          <t>experiment: noSPCP_NBEATS</t>
         </is>
       </c>
     </row>
@@ -11069,7 +12502,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>training data: synthetic (SPCP): VA-generated appliance PCPs</t>
+          <t>training data: synthetic (noSPCP): Ch.5 baseline, copied real PCPs + mapped UPC (own simulation)</t>
         </is>
       </c>
     </row>
@@ -11149,16 +12582,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6034</v>
+        <v>0.5023</v>
       </c>
       <c r="C13" t="n">
-        <v>0.129</v>
+        <v>0.0658</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4069</v>
+        <v>0.3233</v>
       </c>
       <c r="E13" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0372</v>
       </c>
     </row>
     <row r="14">
@@ -11168,16 +12601,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.356</v>
+        <v>1.092</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1451</v>
+        <v>0.0757</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0926</v>
+        <v>1.012</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="15">
@@ -11187,16 +12620,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.8839</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1419</v>
+        <v>0.1482</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4968</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0673</v>
+        <v>0.0723</v>
       </c>
     </row>
     <row r="16">
@@ -11206,16 +12639,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.027</v>
+        <v>1.134</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0761</v>
+        <v>0.0926</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9173</v>
+        <v>0.97</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0549</v>
+        <v>0.0539</v>
       </c>
     </row>
     <row r="17">
@@ -11225,16 +12658,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6349</v>
+        <v>1.2652</v>
       </c>
       <c r="C17" t="n">
-        <v>0.246</v>
+        <v>0.237</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1652</v>
+        <v>1.055</v>
       </c>
       <c r="E17" t="n">
-        <v>0.148</v>
+        <v>0.1983</v>
       </c>
     </row>
     <row r="18">
@@ -11244,16 +12677,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5457</v>
+        <v>0.5585</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0616</v>
+        <v>0.0881</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5274</v>
+        <v>0.5326</v>
       </c>
       <c r="E18" t="n">
-        <v>0.027</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="19">
@@ -11263,16 +12696,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.9721</v>
+        <v>1.3193</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2167</v>
+        <v>0.1125</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3082</v>
+        <v>0.9111</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1175</v>
+        <v>0.09329999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -11282,16 +12715,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9918</v>
+        <v>1.0271</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0805</v>
+        <v>0.0842</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9361</v>
+        <v>1.0122</v>
       </c>
       <c r="E20" t="n">
-        <v>0.027</v>
+        <v>0.0345</v>
       </c>
     </row>
     <row r="21">
@@ -11301,16 +12734,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9579</v>
+        <v>1.0624</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1299</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7416</v>
+        <v>0.8683</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1036</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="22">
@@ -11320,16 +12753,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0473</v>
+        <v>1.025</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0776</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9061</v>
+        <v>0.8917</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0267</v>
+        <v>0.0287</v>
       </c>
     </row>
     <row r="23">
@@ -11339,10 +12772,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0969</v>
+        <v>0.987</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8498</v>
+        <v>0.8108</v>
       </c>
     </row>
     <row r="24">
@@ -11352,10 +12785,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0094</v>
+        <v>1.0447</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9117</v>
+        <v>0.9014</v>
       </c>
     </row>
   </sheetData>
@@ -11382,7 +12815,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>experiment: augmented_NBEATS</t>
+          <t>experiment: SPCP_NBEATS</t>
         </is>
       </c>
     </row>
@@ -11396,7 +12829,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>training data: augmented: noSPCP + SPCP</t>
+          <t>training data: synthetic (SPCP): VA-generated appliance PCPs</t>
         </is>
       </c>
     </row>
@@ -11476,16 +12909,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5757</v>
+        <v>0.5659</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1596</v>
+        <v>0.0646</v>
       </c>
       <c r="D13" t="n">
-        <v>0.387</v>
+        <v>0.3454</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0248</v>
       </c>
     </row>
     <row r="14">
@@ -11495,16 +12928,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1315</v>
+        <v>1.127</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1455</v>
+        <v>0.1098</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9981</v>
+        <v>1.0189</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0692</v>
+        <v>0.0468</v>
       </c>
     </row>
     <row r="15">
@@ -11514,16 +12947,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7688</v>
+        <v>1.0178</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1631</v>
+        <v>0.1703</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4883</v>
+        <v>0.6062</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0706</v>
+        <v>0.09130000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -11533,16 +12966,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1457</v>
+        <v>1.0846</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1374</v>
+        <v>0.1196</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0067</v>
+        <v>0.964</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1063</v>
+        <v>0.0663</v>
       </c>
     </row>
     <row r="17">
@@ -11552,16 +12985,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2855</v>
+        <v>1.3364</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2594</v>
+        <v>0.2049</v>
       </c>
       <c r="D17" t="n">
-        <v>1.014</v>
+        <v>1.1105</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1726</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="18">
@@ -11571,16 +13004,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4806</v>
+        <v>0.5021</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0563</v>
+        <v>0.0443</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.5122</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0239</v>
+        <v>0.0178</v>
       </c>
     </row>
     <row r="19">
@@ -11590,16 +13023,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7304</v>
+        <v>1.3638</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4371</v>
+        <v>0.2202</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1074</v>
+        <v>0.8701</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2493</v>
+        <v>0.0994</v>
       </c>
     </row>
     <row r="20">
@@ -11609,16 +13042,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9991</v>
+        <v>0.9351</v>
       </c>
       <c r="C20" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0492</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9776</v>
+        <v>0.9879</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0413</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="21">
@@ -11628,16 +13061,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9273</v>
+        <v>1.0131</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1441</v>
+        <v>0.1127</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7299</v>
+        <v>0.8408</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1054</v>
+        <v>0.1216</v>
       </c>
     </row>
     <row r="22">
@@ -11647,16 +13080,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9881</v>
+        <v>1.1985</v>
       </c>
       <c r="C22" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0756</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8777</v>
+        <v>0.9731</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0264</v>
+        <v>0.0445</v>
       </c>
     </row>
     <row r="23">
@@ -11666,10 +13099,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0033</v>
+        <v>1.0144</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8089</v>
+        <v>0.8229</v>
       </c>
     </row>
     <row r="24">
@@ -11679,10 +13112,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9936</v>
+        <v>1.0512</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9277</v>
+        <v>0.917</v>
       </c>
     </row>
   </sheetData>
@@ -11709,7 +13142,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>experiment: r+r_NBEATS</t>
+          <t>experiment: augmented_NBEATS</t>
         </is>
       </c>
     </row>
@@ -11723,7 +13156,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>training data: r+r: real duplicated (data-volume control)</t>
+          <t>training data: augmented: noSPCP + SPCP</t>
         </is>
       </c>
     </row>
@@ -11803,16 +13236,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4669</v>
+        <v>0.5112</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0825</v>
+        <v>0.1243</v>
       </c>
       <c r="D13" t="n">
-        <v>0.313</v>
+        <v>0.3326</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0289</v>
+        <v>0.0665</v>
       </c>
     </row>
     <row r="14">
@@ -11822,16 +13255,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0755</v>
+        <v>1.1059</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1065</v>
+        <v>0.1335</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0024</v>
+        <v>0.9972</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0541</v>
+        <v>0.0689</v>
       </c>
     </row>
     <row r="15">
@@ -11841,16 +13274,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8917</v>
+        <v>0.7513</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2498</v>
+        <v>0.1412</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5501</v>
+        <v>0.4905</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1388</v>
+        <v>0.0708</v>
       </c>
     </row>
     <row r="16">
@@ -11860,16 +13293,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.0546</v>
+        <v>1.0987</v>
       </c>
       <c r="C16" t="n">
-        <v>0.076</v>
+        <v>0.1314</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9433</v>
+        <v>0.9586</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0602</v>
+        <v>0.0617</v>
       </c>
     </row>
     <row r="17">
@@ -11879,16 +13312,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2241</v>
+        <v>1.4809</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1849</v>
+        <v>0.2992</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0125</v>
+        <v>1.1934</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1459</v>
+        <v>0.2102</v>
       </c>
     </row>
     <row r="18">
@@ -11898,16 +13331,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4231</v>
+        <v>0.4626</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0439</v>
+        <v>0.0443</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4735</v>
+        <v>0.4991</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0167</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="19">
@@ -11917,16 +13350,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3745</v>
+        <v>1.2969</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1615</v>
+        <v>0.1421</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9181</v>
+        <v>0.8754</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0735</v>
       </c>
     </row>
     <row r="20">
@@ -11936,16 +13369,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0539</v>
+        <v>1.0035</v>
       </c>
       <c r="C20" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0489</v>
       </c>
       <c r="D20" t="n">
-        <v>1.029</v>
+        <v>1.0201</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0304</v>
+        <v>0.0445</v>
       </c>
     </row>
     <row r="21">
@@ -11955,16 +13388,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0876</v>
+        <v>0.9705</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2049</v>
+        <v>0.156</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8626</v>
+        <v>0.7504</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1554</v>
+        <v>0.1243</v>
       </c>
     </row>
     <row r="22">
@@ -11974,16 +13407,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9929</v>
+        <v>1.1043</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0745</v>
+        <v>0.114</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9034</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0219</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="23">
@@ -11993,10 +13426,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9645</v>
+        <v>0.9786</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8008</v>
+        <v>0.8051</v>
       </c>
     </row>
     <row r="24">
@@ -12006,10 +13439,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0543</v>
+        <v>1.0511</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.9046999999999999</v>
       </c>
     </row>
   </sheetData>
